--- a/grupos/6BEM - Estadisticos 20222.xlsx
+++ b/grupos/6BEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="132">
   <si>
     <t>Materia</t>
   </si>
@@ -175,24 +175,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS DE LA SALUD</t>
-  </si>
-  <si>
-    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
-  </si>
-  <si>
-    <t>LITERATURA</t>
-  </si>
-  <si>
-    <t>INTRODUCCIÓN AL DERECHO</t>
-  </si>
-  <si>
-    <t>HISTORIA</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS SOCIALES</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
@@ -918,7 +900,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -972,7 +954,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -995,7 +977,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1049,7 +1031,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>5</v>
@@ -1072,7 +1054,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1126,7 +1108,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1149,7 +1131,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1203,7 +1185,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1226,7 +1208,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1280,7 +1262,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1303,7 +1285,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1357,7 +1339,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>5</v>
@@ -1380,7 +1362,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>8</v>
@@ -1434,7 +1416,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1457,7 +1439,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -1511,7 +1493,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1534,7 +1516,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -1588,7 +1570,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1611,7 +1593,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1665,7 +1647,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1688,7 +1670,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -1742,7 +1724,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1765,7 +1747,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -1819,7 +1801,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>5</v>
@@ -1842,7 +1824,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -1896,7 +1878,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>6</v>
@@ -1919,7 +1901,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -1973,7 +1955,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1996,7 +1978,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -2050,7 +2032,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -2073,7 +2055,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -2127,7 +2109,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2150,7 +2132,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -2204,7 +2186,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2227,7 +2209,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -2281,7 +2263,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2304,7 +2286,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C22">
         <v>8</v>
@@ -2358,7 +2340,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2381,7 +2363,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C23">
         <v>8</v>
@@ -2435,7 +2417,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2458,7 +2440,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -2512,7 +2494,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -2535,7 +2517,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>7</v>
@@ -2589,7 +2571,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2612,7 +2594,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -2666,7 +2648,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>6</v>
@@ -2689,7 +2671,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -2743,7 +2725,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -2766,7 +2748,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -2820,7 +2802,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2843,7 +2825,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -2897,7 +2879,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>5</v>
@@ -2920,7 +2902,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -2974,7 +2956,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -2997,7 +2979,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>7</v>
@@ -3051,7 +3033,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -3184,7 +3166,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>92</v>
@@ -3243,7 +3225,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>80</v>
@@ -3302,7 +3284,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>96</v>
@@ -3361,7 +3343,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>64</v>
@@ -3420,7 +3402,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>96</v>
@@ -3479,7 +3461,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>84</v>
@@ -3538,7 +3520,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>96</v>
@@ -3597,7 +3579,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>92</v>
@@ -3656,7 +3638,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>96</v>
@@ -3715,7 +3697,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>96</v>
@@ -3774,7 +3756,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>80</v>
@@ -3833,7 +3815,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>80</v>
@@ -3892,7 +3874,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>96</v>
@@ -3951,7 +3933,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>96</v>
@@ -4010,7 +3992,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>96</v>
@@ -4069,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>92</v>
@@ -4128,7 +4110,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>92</v>
@@ -4187,7 +4169,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>92</v>
@@ -4246,7 +4228,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>92</v>
@@ -4305,7 +4287,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>92</v>
@@ -4364,7 +4346,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>88</v>
@@ -4423,7 +4405,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>84</v>
@@ -4482,7 +4464,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>96</v>
@@ -4541,7 +4523,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>88</v>
@@ -4600,7 +4582,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>96</v>
@@ -4659,7 +4641,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>92</v>
@@ -4718,7 +4700,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C30">
         <v>92</v>
@@ -4777,7 +4759,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>96</v>
@@ -4843,7 +4825,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
@@ -4883,310 +4865,193 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>52</v>
       </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
       <c r="C2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>32.14</v>
+      </c>
+      <c r="G2">
+        <v>67.86</v>
+      </c>
+      <c r="H2">
+        <v>5.8</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G3">
+        <v>28.57</v>
+      </c>
+      <c r="H3">
+        <v>6.8</v>
       </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G4">
+        <v>14.29</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>89.29000000000001</v>
+      </c>
+      <c r="G5">
+        <v>10.71</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>96.43000000000001</v>
+      </c>
+      <c r="G6">
+        <v>3.57</v>
+      </c>
+      <c r="H6">
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>7.1</v>
+      </c>
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9">
-        <v>28</v>
-      </c>
-      <c r="D9">
-        <v>9</v>
-      </c>
-      <c r="E9">
-        <v>19</v>
-      </c>
-      <c r="F9">
-        <v>32.14</v>
-      </c>
-      <c r="G9">
-        <v>67.86</v>
-      </c>
-      <c r="H9">
-        <v>5.8</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10">
-        <v>28</v>
-      </c>
-      <c r="D10">
-        <v>20</v>
-      </c>
-      <c r="E10">
-        <v>8</v>
-      </c>
-      <c r="F10">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="G10">
-        <v>28.57</v>
-      </c>
-      <c r="H10">
-        <v>6.8</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11">
-        <v>28</v>
-      </c>
-      <c r="D11">
-        <v>24</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="G11">
-        <v>14.29</v>
-      </c>
-      <c r="H11">
-        <v>7.4</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12">
-        <v>28</v>
-      </c>
-      <c r="D12">
-        <v>25</v>
-      </c>
-      <c r="E12">
-        <v>3</v>
-      </c>
-      <c r="F12">
-        <v>89.29000000000001</v>
-      </c>
-      <c r="G12">
-        <v>10.71</v>
-      </c>
-      <c r="H12">
-        <v>7.3</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13">
-        <v>28</v>
-      </c>
-      <c r="D13">
-        <v>27</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>96.43000000000001</v>
-      </c>
-      <c r="G13">
-        <v>3.57</v>
-      </c>
-      <c r="H13">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
+      <c r="J7">
         <v>0</v>
       </c>
     </row>
@@ -5197,7 +5062,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5206,579 +5071,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920039</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920040</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920042</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920043</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920044</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920045</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920046</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920048</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920050</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920051</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920365</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920052</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920053</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920056</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920057</v>
-      </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>124</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920095</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920096</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920097</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920099</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920102</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920058</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920104</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920105</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920062</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>133</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920107</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" t="s">
-        <v>134</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920111</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>135</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920112</v>
-      </c>
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920113</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5797,16 +5105,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>50</v>
@@ -5817,16 +5125,16 @@
         <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5834,16 +5142,16 @@
         <v>20330051920040</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5851,16 +5159,16 @@
         <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5868,16 +5176,16 @@
         <v>20330051920043</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5885,16 +5193,16 @@
         <v>20330051920044</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5902,16 +5210,16 @@
         <v>20330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5919,16 +5227,16 @@
         <v>20330051920046</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5936,16 +5244,16 @@
         <v>20330051920048</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5953,16 +5261,16 @@
         <v>20330051920050</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5970,16 +5278,16 @@
         <v>20330051920051</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5987,16 +5295,16 @@
         <v>20330051920365</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6004,16 +5312,16 @@
         <v>20330051920052</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6021,16 +5329,16 @@
         <v>20330051920053</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6038,16 +5346,16 @@
         <v>20330051920056</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6055,16 +5363,16 @@
         <v>20330051920057</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6072,16 +5380,16 @@
         <v>20330051920095</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6089,16 +5397,16 @@
         <v>20330051920096</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6106,16 +5414,16 @@
         <v>20330051920097</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6123,13 +5431,13 @@
         <v>20330051920099</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6137,16 +5445,16 @@
         <v>20330051920102</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6154,16 +5462,16 @@
         <v>20330051920058</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6171,16 +5479,16 @@
         <v>20330051920104</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6188,16 +5496,16 @@
         <v>20330051920105</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6205,16 +5513,16 @@
         <v>20330051920062</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6222,16 +5530,16 @@
         <v>20330051920107</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6239,16 +5547,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6256,16 +5564,16 @@
         <v>20330051920112</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6273,16 +5581,16 @@
         <v>20330051920113</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6292,7 +5600,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6301,16 +5609,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6324,45 +5632,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920044</v>
+        <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920044</v>
+        <v>20330051920039</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6370,45 +5678,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920045</v>
+        <v>20330051920040</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920045</v>
+        <v>20330051920040</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6416,45 +5724,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920048</v>
+        <v>20330051920046</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920048</v>
+        <v>20330051920046</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6462,45 +5770,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920052</v>
+        <v>20330051920365</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920052</v>
+        <v>20330051920365</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6508,45 +5816,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920057</v>
+        <v>20330051920097</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920057</v>
+        <v>20330051920097</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6554,45 +5862,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920096</v>
+        <v>20330051920058</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920096</v>
+        <v>20330051920058</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6600,45 +5908,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920102</v>
+        <v>20330051920112</v>
       </c>
       <c r="B14" t="s">
         <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920102</v>
+        <v>20330051920112</v>
       </c>
       <c r="B15" t="s">
         <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6646,45 +5954,45 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920107</v>
+        <v>20330051920044</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920107</v>
+        <v>20330051920045</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -6692,45 +6000,45 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920113</v>
+        <v>20330051920048</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920113</v>
+        <v>20330051920052</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -6738,206 +6046,117 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920043</v>
+        <v>20330051920057</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920051</v>
+        <v>20330051920096</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
         <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920053</v>
+        <v>20330051920102</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920056</v>
+        <v>20330051920107</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920095</v>
+        <v>20330051920113</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920099</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920104</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>131</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920105</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" t="s">
-        <v>132</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920062</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" t="s">
-        <v>133</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6BEM - Estadisticos 20222.xlsx
+++ b/grupos/6BEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="135">
   <si>
     <t>Materia</t>
   </si>
@@ -177,10 +177,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Hernández Contreras Ángel</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
   </si>
   <si>
     <t>NC</t>
@@ -4900,7 +4909,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3">
         <v>28</v>
@@ -4932,7 +4941,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>28</v>
@@ -4964,7 +4973,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>28</v>
@@ -4996,7 +5005,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>28</v>
@@ -5028,7 +5037,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C7">
         <v>28</v>
@@ -5071,16 +5080,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5105,16 +5114,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>50</v>
@@ -5125,13 +5134,13 @@
         <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5142,13 +5151,13 @@
         <v>20330051920040</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -5159,13 +5168,13 @@
         <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -5176,13 +5185,13 @@
         <v>20330051920043</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -5193,13 +5202,13 @@
         <v>20330051920044</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5210,13 +5219,13 @@
         <v>20330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5227,13 +5236,13 @@
         <v>20330051920046</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5244,13 +5253,13 @@
         <v>20330051920048</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5261,13 +5270,13 @@
         <v>20330051920050</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -5278,13 +5287,13 @@
         <v>20330051920051</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5295,13 +5304,13 @@
         <v>20330051920365</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -5312,13 +5321,13 @@
         <v>20330051920052</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5329,13 +5338,13 @@
         <v>20330051920053</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5346,13 +5355,13 @@
         <v>20330051920056</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5363,13 +5372,13 @@
         <v>20330051920057</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5380,13 +5389,13 @@
         <v>20330051920095</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5397,13 +5406,13 @@
         <v>20330051920096</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5414,13 +5423,13 @@
         <v>20330051920097</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5431,10 +5440,10 @@
         <v>20330051920099</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5445,13 +5454,13 @@
         <v>20330051920102</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5462,13 +5471,13 @@
         <v>20330051920058</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5479,13 +5488,13 @@
         <v>20330051920104</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5496,13 +5505,13 @@
         <v>20330051920105</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5513,13 +5522,13 @@
         <v>20330051920062</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5530,13 +5539,13 @@
         <v>20330051920107</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5547,13 +5556,13 @@
         <v>20330051920111</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5564,13 +5573,13 @@
         <v>20330051920112</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5581,13 +5590,13 @@
         <v>20330051920113</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5609,16 +5618,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5635,19 +5644,19 @@
         <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5658,13 +5667,13 @@
         <v>20330051920039</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5681,19 +5690,19 @@
         <v>20330051920040</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5704,13 +5713,13 @@
         <v>20330051920040</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5727,19 +5736,19 @@
         <v>20330051920046</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5750,13 +5759,13 @@
         <v>20330051920046</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5773,19 +5782,19 @@
         <v>20330051920365</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5796,13 +5805,13 @@
         <v>20330051920365</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5819,19 +5828,19 @@
         <v>20330051920097</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5842,13 +5851,13 @@
         <v>20330051920097</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5865,19 +5874,19 @@
         <v>20330051920058</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5888,13 +5897,13 @@
         <v>20330051920058</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5911,19 +5920,19 @@
         <v>20330051920112</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5934,13 +5943,13 @@
         <v>20330051920112</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5957,13 +5966,13 @@
         <v>20330051920044</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -5980,13 +5989,13 @@
         <v>20330051920045</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -6003,13 +6012,13 @@
         <v>20330051920048</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -6026,13 +6035,13 @@
         <v>20330051920052</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -6049,13 +6058,13 @@
         <v>20330051920057</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -6072,13 +6081,13 @@
         <v>20330051920096</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -6095,13 +6104,13 @@
         <v>20330051920102</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -6118,13 +6127,13 @@
         <v>20330051920107</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -6141,13 +6150,13 @@
         <v>20330051920113</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>

--- a/grupos/6BEM - Estadisticos 20222.xlsx
+++ b/grupos/6BEM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -204,16 +203,25 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>AMADOR</t>
   </si>
   <si>
-    <t>ANASTACIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>BERNARDO</t>
@@ -222,139 +230,64 @@
     <t>CITALAN</t>
   </si>
   <si>
-    <t>CID</t>
-  </si>
-  <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>GARCÍA</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
     <t>FRANCISCO ALAN</t>
   </si>
   <si>
-    <t>HIRAM FABIAN</t>
-  </si>
-  <si>
-    <t>RAUL</t>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
   </si>
   <si>
     <t>URIEL</t>
@@ -363,64 +296,7 @@
     <t>MISAEL</t>
   </si>
   <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>MARIA ASUNCION</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>CESAR OMAR</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
   </si>
   <si>
     <t>ALEXANDER</t>
@@ -430,6 +306,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -482,11 +361,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -939,10 +819,10 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -975,7 +855,7 @@
         <v>10</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -1016,10 +896,10 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1052,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1093,10 +973,10 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1129,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1170,10 +1050,10 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1247,10 +1127,10 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1283,7 +1163,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1324,10 +1204,10 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1401,10 +1281,10 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1437,7 +1317,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1478,10 +1358,10 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1514,7 +1394,7 @@
         <v>10</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1555,10 +1435,10 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1591,10 +1471,10 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1632,10 +1512,10 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1709,10 +1589,10 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1786,10 +1666,10 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1822,7 +1702,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1863,10 +1743,10 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1899,10 +1779,10 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1940,10 +1820,10 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1976,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2017,10 +1897,10 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2053,10 +1933,10 @@
         <v>10</v>
       </c>
       <c r="X18">
+        <v>10</v>
+      </c>
+      <c r="Y18">
         <v>9</v>
-      </c>
-      <c r="Y18">
-        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2094,10 +1974,10 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2130,10 +2010,10 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2171,10 +2051,10 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2207,10 +2087,10 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2248,10 +2128,10 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2284,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2325,10 +2205,10 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2361,10 +2241,10 @@
         <v>10</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2402,10 +2282,10 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2441,7 +2321,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2479,10 +2359,10 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2515,10 +2395,10 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2556,10 +2436,10 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2595,7 +2475,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2633,10 +2513,10 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2669,10 +2549,10 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2710,10 +2590,10 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2787,10 +2667,10 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2823,10 +2703,10 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2864,10 +2744,10 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2900,7 +2780,7 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -2941,10 +2821,10 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2977,7 +2857,7 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -3018,10 +2898,10 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3054,7 +2934,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3205,10 +3085,10 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3264,10 +3144,10 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3323,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3382,10 +3262,10 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3441,10 +3321,10 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3500,10 +3380,10 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3559,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3618,10 +3498,10 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3677,10 +3557,10 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3736,10 +3616,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3795,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3854,10 +3734,10 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3913,10 +3793,10 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3972,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4031,10 +3911,10 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4090,10 +3970,10 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4149,10 +4029,10 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4208,10 +4088,10 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4267,10 +4147,10 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4326,10 +4206,10 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4385,10 +4265,10 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4444,10 +4324,10 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4503,10 +4383,10 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -4562,10 +4442,10 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4621,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -4680,10 +4560,10 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -4739,10 +4619,10 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -4798,10 +4678,10 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -4838,6 +4718,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4883,24 +4765,24 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>32.14</v>
-      </c>
-      <c r="G2">
-        <v>67.86</v>
+        <v>13</v>
+      </c>
+      <c r="F2" s="2">
+        <v>53.6</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46.4</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4920,11 +4802,11 @@
       <c r="E3">
         <v>8</v>
       </c>
-      <c r="F3">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="G3">
-        <v>28.57</v>
+      <c r="F3" s="2">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G3" s="2">
+        <v>28.6</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -4932,7 +4814,7 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4947,16 +4829,16 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="G4">
-        <v>14.29</v>
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="G4" s="2">
+        <v>17.9</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -4964,7 +4846,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4984,11 +4866,11 @@
       <c r="E5">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>89.29000000000001</v>
-      </c>
-      <c r="G5">
-        <v>10.71</v>
+      <c r="F5" s="2">
+        <v>89.3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10.7</v>
       </c>
       <c r="H5">
         <v>7.3</v>
@@ -4996,7 +4878,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5016,11 +4898,11 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>96.43000000000001</v>
-      </c>
-      <c r="G6">
-        <v>3.57</v>
+      <c r="F6" s="2">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3.6</v>
       </c>
       <c r="H6">
         <v>9.300000000000001</v>
@@ -5028,7 +4910,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5048,10 +4930,10 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
@@ -5060,7 +4942,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5105,511 +4987,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20330051920039</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920040</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920042</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920043</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920044</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920045</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>20330051920046</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920048</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920050</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920051</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920365</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920052</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>20330051920053</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920056</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>20330051920057</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" t="s">
-        <v>121</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920095</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20330051920096</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920097</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920099</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" t="s">
-        <v>125</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20330051920102</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>20330051920058</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>20330051920104</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>20330051920105</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>20330051920062</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" t="s">
-        <v>130</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>20330051920107</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" t="s">
-        <v>131</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>20330051920111</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" t="s">
-        <v>132</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>20330051920112</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" t="s">
-        <v>133</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>20330051920113</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>134</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5641,16 +5019,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920039</v>
+        <v>20330051920040</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5664,16 +5042,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920039</v>
+        <v>20330051920040</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5687,16 +5065,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920040</v>
+        <v>20330051920046</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5710,16 +5088,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920040</v>
+        <v>20330051920046</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5733,16 +5111,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920046</v>
+        <v>20330051920365</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5756,16 +5134,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920046</v>
+        <v>20330051920365</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5779,22 +5157,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920365</v>
+        <v>20330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5802,16 +5180,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920365</v>
+        <v>20330051920097</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5825,22 +5203,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920097</v>
+        <v>20330051920058</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5848,22 +5226,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920097</v>
+        <v>20330051920058</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5871,19 +5249,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920058</v>
+        <v>20330051920111</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>53</v>
@@ -5894,16 +5272,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920058</v>
+        <v>20330051920111</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5920,13 +5298,13 @@
         <v>20330051920112</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -5943,13 +5321,13 @@
         <v>20330051920112</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5966,13 +5344,13 @@
         <v>20330051920044</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -5989,13 +5367,13 @@
         <v>20330051920045</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -6012,13 +5390,13 @@
         <v>20330051920048</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -6032,16 +5410,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920052</v>
+        <v>20330051920113</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -6050,121 +5428,6 @@
         <v>52</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920057</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920096</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920102</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920107</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920113</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6BEM - Estadisticos 20222.xlsx
+++ b/grupos/6BEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -215,24 +215,24 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -248,24 +248,24 @@
     <t>EVARISTO</t>
   </si>
   <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>BELLO</t>
   </si>
   <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -281,22 +281,22 @@
     <t>ALDAIR ALAN</t>
   </si>
   <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
     <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
   </si>
   <si>
     <t>ALEXANDER</t>
@@ -810,13 +810,13 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -887,13 +887,13 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -929,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -964,13 +964,13 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -1003,10 +1003,10 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -1041,13 +1041,13 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1118,13 +1118,13 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1195,13 +1195,13 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -1237,7 +1237,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1272,13 +1272,13 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -1349,13 +1349,13 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>4</v>
@@ -1385,13 +1385,13 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1426,13 +1426,13 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1503,13 +1503,13 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -1539,13 +1539,13 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1580,13 +1580,13 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -1622,7 +1622,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1657,13 +1657,13 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -1734,13 +1734,13 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -1773,10 +1773,10 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1811,13 +1811,13 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -1888,13 +1888,13 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -1965,13 +1965,13 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -2001,10 +2001,10 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2042,13 +2042,13 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>9</v>
@@ -2078,13 +2078,13 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
+        <v>10</v>
+      </c>
+      <c r="W20">
         <v>9</v>
-      </c>
-      <c r="W20">
-        <v>10</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2119,13 +2119,13 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -2155,10 +2155,10 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2196,13 +2196,13 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>8</v>
@@ -2235,7 +2235,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2273,13 +2273,13 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>8</v>
@@ -2312,10 +2312,10 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2350,13 +2350,13 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -2386,13 +2386,13 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2427,13 +2427,13 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>7</v>
@@ -2504,13 +2504,13 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -2540,10 +2540,10 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2581,13 +2581,13 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -2620,7 +2620,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2658,13 +2658,13 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -2697,7 +2697,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2735,13 +2735,13 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>8</v>
@@ -2777,7 +2777,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -2812,13 +2812,13 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>6</v>
@@ -2854,7 +2854,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -2889,13 +2889,13 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>4</v>
@@ -2925,13 +2925,13 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>7</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>6</v>
@@ -3076,13 +3076,13 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3135,13 +3135,13 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L5">
         <v>84</v>
@@ -3194,13 +3194,13 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L6">
         <v>64</v>
@@ -3253,13 +3253,13 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L7">
         <v>80</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>96</v>
@@ -3371,13 +3371,13 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L9">
         <v>72</v>
@@ -3430,13 +3430,13 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>80</v>
@@ -3489,13 +3489,13 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>92</v>
@@ -3548,13 +3548,13 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>96</v>
@@ -3607,13 +3607,13 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L13">
         <v>72</v>
@@ -3666,13 +3666,13 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="L14">
         <v>84</v>
@@ -3725,13 +3725,13 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="L15">
         <v>72</v>
@@ -3784,13 +3784,13 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -3843,13 +3843,13 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>88</v>
@@ -3902,13 +3902,13 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>96</v>
@@ -3961,13 +3961,13 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>96</v>
@@ -4020,13 +4020,13 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>96</v>
@@ -4079,13 +4079,13 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>84</v>
@@ -4138,13 +4138,13 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>96</v>
@@ -4197,13 +4197,13 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -4256,13 +4256,13 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="L24">
         <v>80</v>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="L25">
         <v>92</v>
@@ -4374,13 +4374,13 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>96</v>
@@ -4433,13 +4433,13 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>96</v>
@@ -4492,13 +4492,13 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>80</v>
@@ -4551,13 +4551,13 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>92</v>
@@ -4610,13 +4610,13 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L30">
         <v>96</v>
@@ -4669,13 +4669,13 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>80</v>
@@ -4861,19 +4861,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4905,7 +4905,7 @@
         <v>3.6</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4987,7 +4987,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5203,7 +5203,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920058</v>
+        <v>20330051920111</v>
       </c>
       <c r="B10" t="s">
         <v>65</v>
@@ -5215,7 +5215,7 @@
         <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>53</v>
@@ -5226,7 +5226,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920058</v>
+        <v>20330051920111</v>
       </c>
       <c r="B11" t="s">
         <v>65</v>
@@ -5238,10 +5238,10 @@
         <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5249,7 +5249,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920111</v>
+        <v>20330051920112</v>
       </c>
       <c r="B12" t="s">
         <v>66</v>
@@ -5272,7 +5272,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920111</v>
+        <v>20330051920112</v>
       </c>
       <c r="B13" t="s">
         <v>66</v>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920112</v>
+        <v>20330051920044</v>
       </c>
       <c r="B14" t="s">
         <v>67</v>
@@ -5307,10 +5307,10 @@
         <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5318,16 +5318,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920112</v>
+        <v>20330051920045</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5341,16 +5341,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920044</v>
+        <v>20330051920048</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -5364,22 +5364,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920045</v>
+        <v>20330051920058</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -5387,16 +5387,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920048</v>
+        <v>20330051920113</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -5405,29 +5405,6 @@
         <v>52</v>
       </c>
       <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920113</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6BEM - Estadisticos 20222.xlsx
+++ b/grupos/6BEM - Estadisticos 20222.xlsx
@@ -807,7 +807,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>7</v>
@@ -884,7 +884,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -961,7 +961,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -1038,7 +1038,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -1115,7 +1115,7 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -1192,7 +1192,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -1269,7 +1269,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>7</v>
@@ -1305,7 +1305,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1346,7 +1346,7 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>8</v>
@@ -1423,7 +1423,7 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>8</v>
@@ -1459,7 +1459,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1500,7 +1500,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>5</v>
@@ -1577,7 +1577,7 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -1654,7 +1654,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -1731,7 +1731,7 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -1808,7 +1808,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>8</v>
@@ -1844,7 +1844,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1885,7 +1885,7 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>9</v>
@@ -1921,7 +1921,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -1962,7 +1962,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -1998,7 +1998,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2039,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
         <v>8</v>
@@ -2075,7 +2075,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2116,7 +2116,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -2152,7 +2152,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2193,7 +2193,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -2229,7 +2229,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2270,7 +2270,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -2306,7 +2306,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2347,7 +2347,7 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>7</v>
@@ -2383,7 +2383,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2424,7 +2424,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>6</v>
@@ -2501,7 +2501,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>7</v>
@@ -2578,7 +2578,7 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -2614,7 +2614,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2691,7 +2691,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2732,7 +2732,7 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -2768,7 +2768,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>5</v>
@@ -2809,7 +2809,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>5</v>
@@ -2886,7 +2886,7 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>5</v>
@@ -3073,7 +3073,7 @@
         <v>92</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -3132,7 +3132,7 @@
         <v>92</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I5">
         <v>92</v>
@@ -3191,7 +3191,7 @@
         <v>92</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I6">
         <v>92</v>
@@ -3250,7 +3250,7 @@
         <v>72</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I7">
         <v>96</v>
@@ -3309,7 +3309,7 @@
         <v>92</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -3368,7 +3368,7 @@
         <v>92</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I9">
         <v>92</v>
@@ -3427,7 +3427,7 @@
         <v>92</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -3486,7 +3486,7 @@
         <v>92</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -3545,7 +3545,7 @@
         <v>92</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -3604,7 +3604,7 @@
         <v>92</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I13">
         <v>96</v>
@@ -3663,7 +3663,7 @@
         <v>92</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I14">
         <v>92</v>
@@ -3722,7 +3722,7 @@
         <v>80</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I15">
         <v>88</v>
@@ -3781,7 +3781,7 @@
         <v>92</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I16">
         <v>96</v>
@@ -3840,7 +3840,7 @@
         <v>92</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -3899,7 +3899,7 @@
         <v>92</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -3958,7 +3958,7 @@
         <v>92</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -4017,7 +4017,7 @@
         <v>92</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -4076,7 +4076,7 @@
         <v>92</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I21">
         <v>92</v>
@@ -4135,7 +4135,7 @@
         <v>92</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I22">
         <v>100</v>
@@ -4194,7 +4194,7 @@
         <v>92</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I23">
         <v>100</v>
@@ -4253,7 +4253,7 @@
         <v>92</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -4312,7 +4312,7 @@
         <v>92</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I25">
         <v>96</v>
@@ -4371,7 +4371,7 @@
         <v>92</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -4430,7 +4430,7 @@
         <v>92</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I27">
         <v>92</v>
@@ -4489,7 +4489,7 @@
         <v>92</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I28">
         <v>96</v>
@@ -4548,7 +4548,7 @@
         <v>92</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I29">
         <v>92</v>
@@ -4607,7 +4607,7 @@
         <v>92</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I30">
         <v>88</v>
@@ -4666,7 +4666,7 @@
         <v>92</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I31">
         <v>88</v>
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/6BEM - Estadisticos 20222.xlsx
+++ b/grupos/6BEM - Estadisticos 20222.xlsx
@@ -3058,10 +3058,10 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D4">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -3070,43 +3070,43 @@
         <v>96</v>
       </c>
       <c r="G4">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M4">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3117,10 +3117,10 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E5">
         <v>97.5</v>
@@ -3129,43 +3129,43 @@
         <v>84</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I5">
-        <v>92</v>
+        <v>87.8</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K5">
-        <v>80</v>
+        <v>88.8</v>
       </c>
       <c r="L5">
         <v>84</v>
       </c>
       <c r="M5">
-        <v>88</v>
+        <v>91.8</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>88.8</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3176,10 +3176,10 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>87.5</v>
@@ -3188,43 +3188,43 @@
         <v>96</v>
       </c>
       <c r="G6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I6">
-        <v>92</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
+        <v>83.8</v>
+      </c>
+      <c r="L6">
         <v>80</v>
       </c>
-      <c r="L6">
-        <v>64</v>
-      </c>
       <c r="M6">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>83.8</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3235,10 +3235,10 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>64</v>
+        <v>66.7</v>
       </c>
       <c r="D7">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="E7">
         <v>80</v>
@@ -3247,43 +3247,43 @@
         <v>52</v>
       </c>
       <c r="G7">
-        <v>72</v>
+        <v>78.3</v>
       </c>
       <c r="H7">
-        <v>120</v>
+        <v>61.8</v>
       </c>
       <c r="I7">
-        <v>96</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="K7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L7">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="M7">
-        <v>84</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>61.8</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3294,10 +3294,10 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -3306,10 +3306,10 @@
         <v>96</v>
       </c>
       <c r="G8">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -3324,25 +3324,25 @@
         <v>96</v>
       </c>
       <c r="M8">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3353,10 +3353,10 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="D9">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="E9">
         <v>95</v>
@@ -3365,43 +3365,43 @@
         <v>92</v>
       </c>
       <c r="G9">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>92</v>
+        <v>89.8</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="K9">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="L9">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="M9">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>89.8</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3412,10 +3412,10 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>92.5</v>
@@ -3424,10 +3424,10 @@
         <v>84</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -3436,31 +3436,31 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="L10">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M10">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3471,10 +3471,10 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D11">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E11">
         <v>95</v>
@@ -3483,43 +3483,43 @@
         <v>92</v>
       </c>
       <c r="G11">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L11">
         <v>92</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3530,10 +3530,10 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -3542,10 +3542,10 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -3557,28 +3557,28 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M12">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3589,10 +3589,10 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>85</v>
@@ -3601,43 +3601,43 @@
         <v>72</v>
       </c>
       <c r="G13">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I13">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="L13">
         <v>72</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3648,10 +3648,10 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="D14">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E14">
         <v>80</v>
@@ -3660,43 +3660,43 @@
         <v>80</v>
       </c>
       <c r="G14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I14">
-        <v>92</v>
+        <v>87.8</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K14">
-        <v>97.5</v>
+        <v>88.8</v>
       </c>
       <c r="L14">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>88.8</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3707,10 +3707,10 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E15">
         <v>90</v>
@@ -3719,43 +3719,43 @@
         <v>80</v>
       </c>
       <c r="G15">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I15">
-        <v>88</v>
+        <v>85.7</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K15">
-        <v>82.5</v>
+        <v>86.3</v>
       </c>
       <c r="L15">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M15">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>86.3</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3766,10 +3766,10 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -3778,13 +3778,13 @@
         <v>100</v>
       </c>
       <c r="G16">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I16">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -3796,25 +3796,25 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3825,10 +3825,10 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>100</v>
@@ -3837,10 +3837,10 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -3852,28 +3852,28 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M17">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3884,10 +3884,10 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -3896,10 +3896,10 @@
         <v>96</v>
       </c>
       <c r="G18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -3914,25 +3914,25 @@
         <v>96</v>
       </c>
       <c r="M18">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3943,10 +3943,10 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D19">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E19">
         <v>87.5</v>
@@ -3955,43 +3955,43 @@
         <v>80</v>
       </c>
       <c r="G19">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="L19">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="M19">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4002,10 +4002,10 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D20">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E20">
         <v>97.5</v>
@@ -4014,43 +4014,43 @@
         <v>92</v>
       </c>
       <c r="G20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="L20">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M20">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4061,55 +4061,55 @@
         <v>100</v>
       </c>
       <c r="C21">
+        <v>95.8</v>
+      </c>
+      <c r="D21">
+        <v>95.8</v>
+      </c>
+      <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21">
+        <v>100</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="J21">
+        <v>97.7</v>
+      </c>
+      <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
         <v>92</v>
       </c>
-      <c r="D21">
-        <v>115</v>
-      </c>
-      <c r="E21">
-        <v>100</v>
-      </c>
-      <c r="F21">
-        <v>100</v>
-      </c>
-      <c r="G21">
+      <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
+        <v>100</v>
+      </c>
+      <c r="O21">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="P21">
+        <v>97.7</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>92</v>
       </c>
-      <c r="H21">
-        <v>120</v>
-      </c>
-      <c r="I21">
-        <v>92</v>
-      </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
-      <c r="L21">
-        <v>84</v>
-      </c>
-      <c r="M21">
-        <v>104</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4120,10 +4120,10 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D22">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E22">
         <v>97.5</v>
@@ -4132,43 +4132,43 @@
         <v>96</v>
       </c>
       <c r="G22">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J22">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="L22">
         <v>96</v>
       </c>
       <c r="M22">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4179,10 +4179,10 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D23">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E23">
         <v>85</v>
@@ -4191,43 +4191,43 @@
         <v>76</v>
       </c>
       <c r="G23">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K23">
-        <v>97.5</v>
+        <v>91.3</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4238,10 +4238,10 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="D24">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E24">
         <v>87.5</v>
@@ -4250,43 +4250,43 @@
         <v>72</v>
       </c>
       <c r="G24">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K24">
-        <v>92.5</v>
+        <v>90</v>
       </c>
       <c r="L24">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4297,10 +4297,10 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="D25">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="E25">
         <v>92.5</v>
@@ -4309,43 +4309,43 @@
         <v>96</v>
       </c>
       <c r="G25">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I25">
-        <v>96</v>
+        <v>91.8</v>
       </c>
       <c r="J25">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="K25">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="L25">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4356,10 +4356,10 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -4368,43 +4368,43 @@
         <v>88</v>
       </c>
       <c r="G26">
+        <v>100</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
         <v>92</v>
       </c>
-      <c r="H26">
-        <v>120</v>
-      </c>
-      <c r="I26">
-        <v>100</v>
-      </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
-      <c r="L26">
-        <v>96</v>
-      </c>
       <c r="M26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4415,10 +4415,10 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="D27">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E27">
         <v>92.5</v>
@@ -4427,43 +4427,43 @@
         <v>96</v>
       </c>
       <c r="G27">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I27">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="L27">
         <v>96</v>
       </c>
       <c r="M27">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4474,10 +4474,10 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -4486,13 +4486,13 @@
         <v>96</v>
       </c>
       <c r="G28">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I28">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -4501,28 +4501,28 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="M28">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4533,10 +4533,10 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D29">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -4545,43 +4545,43 @@
         <v>100</v>
       </c>
       <c r="G29">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I29">
-        <v>92</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J29">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4592,10 +4592,10 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="D30">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E30">
         <v>90</v>
@@ -4604,43 +4604,43 @@
         <v>88</v>
       </c>
       <c r="G30">
+        <v>100</v>
+      </c>
+      <c r="H30">
+        <v>100</v>
+      </c>
+      <c r="I30">
+        <v>91.8</v>
+      </c>
+      <c r="J30">
+        <v>97.7</v>
+      </c>
+      <c r="K30">
+        <v>85</v>
+      </c>
+      <c r="L30">
         <v>92</v>
       </c>
-      <c r="H30">
-        <v>120</v>
-      </c>
-      <c r="I30">
-        <v>88</v>
-      </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
-      <c r="K30">
-        <v>80</v>
-      </c>
-      <c r="L30">
-        <v>96</v>
-      </c>
       <c r="M30">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4651,10 +4651,10 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>97.5</v>
@@ -4663,43 +4663,43 @@
         <v>92</v>
       </c>
       <c r="G31">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I31">
-        <v>88</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="L31">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="M31">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6BEM - Estadisticos 20222.xlsx
+++ b/grupos/6BEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="61">
   <si>
     <t>Materia</t>
   </si>
@@ -176,21 +176,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Hernández Contreras Ángel</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -201,105 +201,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -825,22 +726,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -902,40 +803,40 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>7</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -979,28 +880,28 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>7</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1009,10 +910,10 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1056,34 +957,34 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1133,22 +1034,22 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1163,10 +1064,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1210,40 +1111,40 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>7</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1287,31 +1188,31 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1320,7 +1221,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1364,22 +1265,22 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1391,13 +1292,13 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1441,25 +1342,25 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1518,22 +1419,22 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1545,13 +1446,13 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1595,40 +1496,40 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>7</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1672,40 +1573,40 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>7</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1749,22 +1650,22 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -1773,7 +1674,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1782,7 +1683,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1826,25 +1727,25 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1859,7 +1760,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1903,25 +1804,25 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -1980,22 +1881,22 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2013,7 +1914,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2057,25 +1958,25 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2134,25 +2035,25 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2167,7 +2068,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2211,25 +2112,25 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2241,7 +2142,7 @@
         <v>10</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2288,31 +2189,31 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>8</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2321,7 +2222,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2365,40 +2266,40 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>7</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>7</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2442,22 +2343,22 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2466,10 +2367,10 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2519,28 +2420,28 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>7</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2596,22 +2497,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2673,25 +2574,25 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2706,7 +2607,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2750,40 +2651,40 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2827,28 +2728,28 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>7</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -2860,7 +2761,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2904,22 +2805,22 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>7</v>
@@ -2937,7 +2838,7 @@
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3094,16 +2995,16 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="P4">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="R4">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3153,19 +3054,19 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>87.8</v>
+        <v>90</v>
       </c>
       <c r="P5">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="Q5">
-        <v>88.8</v>
+        <v>87.5</v>
       </c>
       <c r="R5">
-        <v>84</v>
+        <v>86.7</v>
       </c>
       <c r="S5">
-        <v>91.8</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3212,19 +3113,19 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>95.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="P6">
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>83.8</v>
+        <v>87.5</v>
       </c>
       <c r="R6">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="S6">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3268,22 +3169,22 @@
         <v>79.59999999999999</v>
       </c>
       <c r="N7">
-        <v>61.8</v>
+        <v>73.8</v>
       </c>
       <c r="O7">
-        <v>81.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="P7">
-        <v>81.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R7">
-        <v>66</v>
+        <v>77.3</v>
       </c>
       <c r="S7">
-        <v>79.59999999999999</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3330,16 +3231,16 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="R8">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3389,16 +3290,16 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>89.8</v>
+        <v>91.3</v>
       </c>
       <c r="P9">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q9">
-        <v>92.5</v>
+        <v>93</v>
       </c>
       <c r="R9">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3448,19 +3349,19 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q10">
-        <v>96.3</v>
+        <v>97.7</v>
       </c>
       <c r="R10">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="S10">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3507,19 +3408,19 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="P11">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q11">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R11">
-        <v>92</v>
+        <v>94.7</v>
       </c>
       <c r="S11">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3575,7 +3476,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3625,19 +3526,19 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q13">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R13">
-        <v>72</v>
+        <v>81.3</v>
       </c>
       <c r="S13">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3684,19 +3585,19 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>87.8</v>
+        <v>90</v>
       </c>
       <c r="P14">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="Q14">
-        <v>88.8</v>
+        <v>87.5</v>
       </c>
       <c r="R14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="S14">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3743,19 +3644,19 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>85.7</v>
+        <v>90</v>
       </c>
       <c r="P15">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="Q15">
-        <v>86.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R15">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="S15">
-        <v>83.7</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3802,7 +3703,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -3814,7 +3715,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3867,10 +3768,10 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="R17">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -3929,7 +3830,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -3979,19 +3880,19 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="P19">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q19">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="R19">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="S19">
-        <v>95.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4038,16 +3939,16 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="P20">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q20">
-        <v>98.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R20">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -4097,16 +3998,16 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>93.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="P21">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q21">
         <v>100</v>
       </c>
       <c r="R21">
-        <v>92</v>
+        <v>94.7</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -4156,16 +4057,16 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="P22">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q22">
-        <v>98.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R22">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4215,19 +4116,19 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P23">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q23">
-        <v>91.3</v>
+        <v>94.5</v>
       </c>
       <c r="R23">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="S23">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4274,19 +4175,19 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>95.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="P24">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q24">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R24">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="S24">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4333,19 +4234,19 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>91.8</v>
+        <v>91.3</v>
       </c>
       <c r="P25">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="Q25">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R25">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S25">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4392,7 +4293,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4401,10 +4302,10 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>92</v>
+        <v>94.7</v>
       </c>
       <c r="S26">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4451,16 +4352,16 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>91.8</v>
+        <v>95</v>
       </c>
       <c r="P27">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q27">
-        <v>96.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R27">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -4510,16 +4411,16 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -4569,19 +4470,19 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>93.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="P29">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="R29">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="S29">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4628,16 +4529,16 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>91.8</v>
+        <v>91.3</v>
       </c>
       <c r="P30">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q30">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="R30">
-        <v>92</v>
+        <v>94.7</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -4687,19 +4588,19 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>93.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q31">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="R31">
-        <v>86</v>
+        <v>90.7</v>
       </c>
       <c r="S31">
-        <v>95.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4756,7 +4657,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
@@ -4765,19 +4666,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>53.6</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>46.4</v>
+        <v>3.6</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4788,7 +4689,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -4797,19 +4698,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>71.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>28.6</v>
+        <v>3.6</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4820,7 +4721,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -4829,19 +4730,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>82.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>17.9</v>
+        <v>3.6</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4852,28 +4753,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5">
         <v>28</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4884,7 +4785,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -4893,19 +4794,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4916,7 +4817,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -4937,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4987,7 +4888,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5017,397 +4918,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920040</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920040</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920046</v>
-      </c>
-      <c r="B4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920046</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920365</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920365</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920097</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920097</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920111</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920111</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920112</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920112</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920044</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920045</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920048</v>
-      </c>
-      <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920058</v>
-      </c>
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920113</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/6BEM - Estadisticos 20222.xlsx
+++ b/grupos/6BEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="64">
   <si>
     <t>Materia</t>
   </si>
@@ -176,15 +176,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
@@ -201,6 +201,15 @@
   </si>
   <si>
     <t>Nombres</t>
+  </si>
+  <si>
+    <t>ANASTACIO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
   </si>
 </sst>
 </file>
@@ -987,7 +996,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -3163,7 +3172,7 @@
         <v>85</v>
       </c>
       <c r="L7">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="M7">
         <v>79.59999999999999</v>
@@ -3181,7 +3190,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="R7">
-        <v>77.3</v>
+        <v>84</v>
       </c>
       <c r="S7">
         <v>80.3</v>
@@ -4657,7 +4666,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
@@ -4678,7 +4687,7 @@
         <v>3.6</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4689,7 +4698,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -4710,7 +4719,7 @@
         <v>3.6</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4721,7 +4730,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -4730,19 +4739,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4888,7 +4897,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4918,6 +4927,52 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920042</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920042</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
